--- a/2026-2027-IT.xlsx
+++ b/2026-2027-IT.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8196" tabRatio="500"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8196" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="ИТ_5" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="93">
   <si>
     <t>#</t>
   </si>
@@ -300,6 +300,9 @@
   </si>
   <si>
     <t>Docker - внутреннее устройство</t>
+  </si>
+  <si>
+    <t>Tailwind</t>
   </si>
 </sst>
 </file>
@@ -427,7 +430,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -454,9 +457,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
@@ -1145,60 +1145,75 @@
     </row>
     <row r="24" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>1</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>5</v>
+        <v>22</v>
+      </c>
+      <c r="B24" t="s">
+        <v>28</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>6</v>
+        <v>29</v>
+      </c>
+      <c r="D24">
+        <v>14</v>
+      </c>
+      <c r="E24" t="s">
+        <v>92</v>
       </c>
       <c r="G24">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>2</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>7</v>
+        <v>28</v>
+      </c>
+      <c r="B25" t="s">
+        <v>35</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G25">
-        <v>4</v>
+        <v>29</v>
+      </c>
+      <c r="D25">
+        <v>14</v>
+      </c>
+      <c r="E25" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="26" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>6</v>
+      </c>
+      <c r="G26">
+        <v>4</v>
       </c>
     </row>
     <row r="27" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>6</v>
+      </c>
+      <c r="G27">
+        <v>4</v>
       </c>
     </row>
     <row r="28" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>6</v>
@@ -1206,63 +1221,57 @@
     </row>
     <row r="29" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="G29">
-        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="G31">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="G32">
-        <v>1</v>
-      </c>
     </row>
     <row r="33" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>18</v>
@@ -1273,57 +1282,60 @@
     </row>
     <row r="34" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="G34">
+        <v>1</v>
+      </c>
     </row>
     <row r="35" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A35">
+        <v>15</v>
+      </c>
+      <c r="B35" s="2" t="s">
         <v>21</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="G35">
+        <v>1</v>
+      </c>
     </row>
     <row r="36" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>22</v>
-      </c>
-      <c r="B36" t="s">
-        <v>28</v>
+        <v>17</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="G36">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="37" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>24</v>
-      </c>
-      <c r="B37" t="s">
-        <v>31</v>
+        <v>21</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
     </row>
     <row r="38" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B38" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>29</v>
@@ -1458,10 +1470,10 @@
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.21875" customWidth="1"/>
-    <col min="2" max="2" width="34.109375" customWidth="1"/>
+    <col min="2" max="2" width="36.6640625" customWidth="1"/>
     <col min="3" max="3" width="14.109375" customWidth="1"/>
-    <col min="4" max="4" width="19.77734375" customWidth="1"/>
-    <col min="5" max="5" width="42.6640625" customWidth="1"/>
+    <col min="4" max="4" width="28" customWidth="1"/>
+    <col min="5" max="5" width="39.88671875" customWidth="1"/>
     <col min="6" max="6" width="16.33203125" style="10" customWidth="1"/>
     <col min="7" max="7" width="14.88671875" style="10" customWidth="1"/>
     <col min="8" max="8" width="13.33203125" style="10" customWidth="1"/>
@@ -1497,7 +1509,7 @@
       <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="3" t="s">
         <v>4</v>
       </c>
       <c r="E1" s="4" t="s">
@@ -1621,7 +1633,7 @@
       <c r="E6" t="s">
         <v>80</v>
       </c>
-      <c r="H6" s="13">
+      <c r="H6" s="12">
         <v>3</v>
       </c>
     </row>
@@ -1641,7 +1653,7 @@
       <c r="E7" t="s">
         <v>80</v>
       </c>
-      <c r="H7" s="13">
+      <c r="H7" s="12">
         <v>3</v>
       </c>
     </row>
@@ -1885,7 +1897,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:10" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" s="13" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="11">
         <v>44</v>
       </c>
@@ -1899,7 +1911,7 @@
       <c r="E20" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="J20" s="14">
+      <c r="J20" s="13">
         <v>1</v>
       </c>
     </row>
@@ -1965,32 +1977,50 @@
     </row>
     <row r="24" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>1</v>
-      </c>
-      <c r="B24" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" t="s">
+        <v>28</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D24">
+        <v>14</v>
+      </c>
+      <c r="E24" t="s">
+        <v>92</v>
+      </c>
+      <c r="I24" s="10">
         <v>5</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>2</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>7</v>
+        <v>28</v>
+      </c>
+      <c r="B25" t="s">
+        <v>35</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>6</v>
+        <v>29</v>
+      </c>
+      <c r="D25">
+        <v>14</v>
+      </c>
+      <c r="E25" t="s">
+        <v>92</v>
+      </c>
+      <c r="I25" s="10">
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>6</v>
@@ -1998,10 +2028,10 @@
     </row>
     <row r="27" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>6</v>
@@ -2009,10 +2039,10 @@
     </row>
     <row r="28" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>6</v>
@@ -2020,10 +2050,10 @@
     </row>
     <row r="29" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>6</v>
@@ -2031,32 +2061,32 @@
     </row>
     <row r="30" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>18</v>
@@ -2064,10 +2094,10 @@
     </row>
     <row r="33" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>18</v>
@@ -2075,10 +2105,10 @@
     </row>
     <row r="34" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>18</v>
@@ -2086,10 +2116,10 @@
     </row>
     <row r="35" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35">
+        <v>15</v>
+      </c>
+      <c r="B35" s="2" t="s">
         <v>21</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>18</v>
@@ -2097,32 +2127,32 @@
     </row>
     <row r="36" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>22</v>
-      </c>
-      <c r="B36" t="s">
-        <v>28</v>
+        <v>17</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>24</v>
-      </c>
-      <c r="B37" t="s">
-        <v>31</v>
+        <v>21</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B38" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>29</v>

--- a/2026-2027-IT.xlsx
+++ b/2026-2027-IT.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="95">
   <si>
     <t>#</t>
   </si>
@@ -303,6 +303,12 @@
   </si>
   <si>
     <t>Tailwind</t>
+  </si>
+  <si>
+    <t>graphQL</t>
+  </si>
+  <si>
+    <t>Nginx - установка и настройка</t>
   </si>
 </sst>
 </file>
@@ -1182,30 +1188,42 @@
     </row>
     <row r="26" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A26">
+        <v>13</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D26">
+        <v>15</v>
+      </c>
+      <c r="E26" t="s">
+        <v>93</v>
+      </c>
+      <c r="G26">
         <v>1</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G26">
-        <v>4</v>
       </c>
     </row>
     <row r="27" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>6</v>
+        <v>18</v>
+      </c>
+      <c r="D27">
+        <v>15</v>
+      </c>
+      <c r="E27" t="s">
+        <v>93</v>
       </c>
       <c r="G27">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:31" x14ac:dyDescent="0.25">
@@ -1218,80 +1236,92 @@
       <c r="C28" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D28">
+        <v>16</v>
+      </c>
+      <c r="E28" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="29" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>6</v>
+      </c>
+      <c r="D29">
+        <v>16</v>
+      </c>
+      <c r="E29" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="30" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>6</v>
+      </c>
+      <c r="G30">
+        <v>4</v>
       </c>
     </row>
     <row r="31" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G31">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="G33">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="G34">
-        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:31" x14ac:dyDescent="0.25">
@@ -1474,12 +1504,12 @@
     <col min="3" max="3" width="14.109375" customWidth="1"/>
     <col min="4" max="4" width="28" customWidth="1"/>
     <col min="5" max="5" width="39.88671875" customWidth="1"/>
-    <col min="6" max="6" width="16.33203125" style="10" customWidth="1"/>
+    <col min="6" max="6" width="14.109375" style="10" customWidth="1"/>
     <col min="7" max="7" width="14.88671875" style="10" customWidth="1"/>
-    <col min="8" max="8" width="13.33203125" style="10" customWidth="1"/>
-    <col min="9" max="9" width="15.44140625" style="10" customWidth="1"/>
-    <col min="10" max="10" width="12.88671875" style="10" customWidth="1"/>
-    <col min="11" max="11" width="11.5546875" style="10" customWidth="1"/>
+    <col min="8" max="8" width="14.5546875" style="10" customWidth="1"/>
+    <col min="9" max="9" width="13.44140625" style="10" customWidth="1"/>
+    <col min="10" max="10" width="13.6640625" style="10" customWidth="1"/>
+    <col min="11" max="11" width="15" style="10" customWidth="1"/>
     <col min="12" max="12" width="13.6640625" style="10" customWidth="1"/>
     <col min="13" max="13" width="28.33203125" style="10" customWidth="1"/>
     <col min="14" max="14" width="20.109375" style="10" customWidth="1"/>
@@ -2017,24 +2047,42 @@
     </row>
     <row r="26" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="B26" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D26">
+        <v>15</v>
+      </c>
+      <c r="E26" t="s">
+        <v>93</v>
+      </c>
+      <c r="H26" s="10">
         <v>5</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>6</v>
+        <v>18</v>
+      </c>
+      <c r="D27">
+        <v>15</v>
+      </c>
+      <c r="E27" t="s">
+        <v>93</v>
+      </c>
+      <c r="H27" s="10">
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2047,24 +2095,42 @@
       <c r="C28" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D28">
+        <v>16</v>
+      </c>
+      <c r="E28" t="s">
+        <v>94</v>
+      </c>
+      <c r="H28" s="10">
+        <v>6</v>
+      </c>
     </row>
     <row r="29" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C29" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D29">
+        <v>16</v>
+      </c>
+      <c r="E29" t="s">
+        <v>94</v>
+      </c>
+      <c r="H29" s="10">
         <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>6</v>
@@ -2072,10 +2138,10 @@
     </row>
     <row r="31" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>6</v>
@@ -2083,32 +2149,32 @@
     </row>
     <row r="32" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>18</v>

--- a/2026-2027-IT.xlsx
+++ b/2026-2027-IT.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8196" tabRatio="500" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8196" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="ИТ_5" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="96">
   <si>
     <t>#</t>
   </si>
@@ -309,6 +309,9 @@
   </si>
   <si>
     <t>Nginx - установка и настройка</t>
+  </si>
+  <si>
+    <t>Redis</t>
   </si>
 </sst>
 </file>
@@ -1262,24 +1265,27 @@
     </row>
     <row r="30" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>1</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>5</v>
+        <v>43</v>
+      </c>
+      <c r="B30" t="s">
+        <v>50</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G30">
-        <v>4</v>
+        <v>29</v>
+      </c>
+      <c r="D30">
+        <v>17</v>
+      </c>
+      <c r="E30" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="31" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>6</v>
@@ -1290,71 +1296,74 @@
     </row>
     <row r="32" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>6</v>
+      </c>
+      <c r="G32">
+        <v>4</v>
       </c>
     </row>
     <row r="33" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="G33">
-        <v>7</v>
       </c>
     </row>
     <row r="34" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>18</v>
+        <v>6</v>
+      </c>
+      <c r="G34">
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="G35">
-        <v>1</v>
-      </c>
     </row>
     <row r="36" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="G36">
+        <v>1</v>
+      </c>
     </row>
     <row r="37" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>18</v>
@@ -1362,21 +1371,21 @@
     </row>
     <row r="38" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>24</v>
-      </c>
-      <c r="B38" t="s">
-        <v>31</v>
+        <v>21</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
     </row>
     <row r="39" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B39" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>29</v>
@@ -1384,10 +1393,10 @@
     </row>
     <row r="40" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B40" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>29</v>
@@ -1395,35 +1404,35 @@
     </row>
     <row r="41" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B41" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="G41">
-        <v>4</v>
       </c>
     </row>
     <row r="42" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B42" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>29</v>
+      </c>
+      <c r="G42">
+        <v>4</v>
       </c>
     </row>
     <row r="43" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B43" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>29</v>
@@ -1431,10 +1440,10 @@
     </row>
     <row r="44" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B44" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>29</v>
@@ -1442,10 +1451,10 @@
     </row>
     <row r="45" spans="1:31" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B45" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>29</v>
@@ -2127,21 +2136,30 @@
     </row>
     <row r="30" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>1</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>5</v>
+        <v>43</v>
+      </c>
+      <c r="B30" t="s">
+        <v>50</v>
       </c>
       <c r="C30" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D30">
+        <v>17</v>
+      </c>
+      <c r="E30" t="s">
+        <v>95</v>
+      </c>
+      <c r="I30" s="10">
         <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>6</v>
@@ -2149,10 +2167,10 @@
     </row>
     <row r="32" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>6</v>
@@ -2160,10 +2178,10 @@
     </row>
     <row r="33" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>6</v>
@@ -2171,21 +2189,21 @@
     </row>
     <row r="34" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>18</v>
@@ -2193,10 +2211,10 @@
     </row>
     <row r="36" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>18</v>
@@ -2204,10 +2222,10 @@
     </row>
     <row r="37" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>18</v>
@@ -2215,21 +2233,21 @@
     </row>
     <row r="38" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>24</v>
-      </c>
-      <c r="B38" t="s">
-        <v>31</v>
+        <v>21</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B39" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>29</v>
@@ -2237,10 +2255,10 @@
     </row>
     <row r="40" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B40" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>29</v>
@@ -2248,10 +2266,10 @@
     </row>
     <row r="41" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B41" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>29</v>
@@ -2259,10 +2277,10 @@
     </row>
     <row r="42" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B42" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>29</v>
@@ -2270,10 +2288,10 @@
     </row>
     <row r="43" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B43" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>29</v>
@@ -2281,10 +2299,10 @@
     </row>
     <row r="44" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B44" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>29</v>
@@ -2292,10 +2310,10 @@
     </row>
     <row r="45" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B45" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>29</v>

--- a/2026-2027-IT.xlsx
+++ b/2026-2027-IT.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8196" tabRatio="500"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8196" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="ИТ_5" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="96">
   <si>
     <t>#</t>
   </si>
@@ -439,9 +439,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -609,232 +608,205 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:31" ht="29.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="M1" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="N1" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="O1" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="P1" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="Q1" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="R1" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="S1" s="5" t="s">
+      <c r="S1" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="T1" s="5" t="s">
+      <c r="T1" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="U1" s="4" t="s">
+      <c r="U1" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="V1" s="4" t="s">
+      <c r="V1" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="W1" s="4" t="s">
+      <c r="W1" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="X1" s="5" t="s">
+      <c r="X1" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="Y1" s="4" t="s">
+      <c r="Y1" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="Z1" s="4" t="s">
+      <c r="Z1" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="AA1" s="4" t="s">
+      <c r="AA1" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="AB1" s="6" t="s">
+      <c r="AB1" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="AC1" s="6" t="s">
+      <c r="AC1" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="AD1" s="6" t="s">
+      <c r="AD1" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="AE1" s="6" t="s">
+      <c r="AE1" s="5" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2" t="s">
-        <v>78</v>
+        <v>5</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3" t="s">
-        <v>78</v>
+        <v>7</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G3">
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>18</v>
+        <v>8</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="E4" t="s">
-        <v>79</v>
-      </c>
-      <c r="G4">
-        <v>3</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>20</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>18</v>
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E5" t="s">
-        <v>79</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>8</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6">
-        <v>3</v>
-      </c>
-      <c r="E6" t="s">
-        <v>80</v>
-      </c>
-      <c r="G6">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D7">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="E7" t="s">
-        <v>80</v>
-      </c>
-      <c r="G7">
-        <v>6</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D8">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E8" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G8">
         <v>7</v>
@@ -842,656 +814,634 @@
     </row>
     <row r="9" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>25</v>
-      </c>
-      <c r="B9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>29</v>
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="D9">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E9" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G9">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>33</v>
-      </c>
-      <c r="B10" t="s">
-        <v>40</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>29</v>
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="D10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G10">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>40</v>
-      </c>
-      <c r="B11" t="s">
-        <v>47</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>29</v>
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="D11">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="G11">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>42</v>
-      </c>
-      <c r="B12" t="s">
-        <v>49</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>29</v>
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="D12">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E12" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G12">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>4</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D13">
-        <v>7</v>
-      </c>
-      <c r="E13" t="s">
-        <v>84</v>
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>7</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>6</v>
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="D14">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E14" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="G14">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>37</v>
-      </c>
-      <c r="B15" t="s">
-        <v>44</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>29</v>
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="D15">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E15" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="G15">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17" t="s">
+        <v>78</v>
+      </c>
+      <c r="G17">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D19">
+        <v>2</v>
+      </c>
+      <c r="E19" t="s">
+        <v>79</v>
+      </c>
+      <c r="G19">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C21" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D21">
+        <v>2</v>
+      </c>
+      <c r="E21" t="s">
+        <v>79</v>
+      </c>
+      <c r="G21">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>28</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D23">
+        <v>14</v>
+      </c>
+      <c r="E23" t="s">
+        <v>92</v>
+      </c>
+      <c r="G23">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>30</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D24">
+        <v>10</v>
+      </c>
+      <c r="E24" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D26">
+        <v>5</v>
+      </c>
+      <c r="E26" t="s">
+        <v>82</v>
+      </c>
+      <c r="G26">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
         <v>33</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D16">
+      <c r="C27" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D27">
         <v>9</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E27" t="s">
         <v>89</v>
       </c>
-      <c r="G16">
+      <c r="G27">
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A17">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28">
         <v>27</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B28" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D17">
+      <c r="C28" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D28">
         <v>9</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E28" t="s">
         <v>89</v>
       </c>
-      <c r="G17">
+      <c r="G28">
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>23</v>
-      </c>
-      <c r="B18" t="s">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>35</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D29">
+        <v>14</v>
+      </c>
+      <c r="E29" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>36</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31">
         <v>30</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D18">
+      <c r="B31" t="s">
+        <v>37</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>38</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D32">
+        <v>13</v>
+      </c>
+      <c r="E32" t="s">
+        <v>91</v>
+      </c>
+      <c r="G32">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>39</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G33">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>40</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D34">
+        <v>5</v>
+      </c>
+      <c r="E34" t="s">
+        <v>82</v>
+      </c>
+      <c r="G34">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>41</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>42</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>43</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D37">
+        <v>12</v>
+      </c>
+      <c r="E37" t="s">
+        <v>90</v>
+      </c>
+      <c r="G37">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>44</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D38">
+        <v>8</v>
+      </c>
+      <c r="E38" t="s">
+        <v>85</v>
+      </c>
+      <c r="G38">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>45</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D39">
+        <v>13</v>
+      </c>
+      <c r="E39" t="s">
+        <v>91</v>
+      </c>
+      <c r="G39">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
+        <v>46</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D40">
         <v>10</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E40" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>39</v>
-      </c>
-      <c r="B19" t="s">
-        <v>46</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D19">
-        <v>10</v>
-      </c>
-      <c r="E19" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A20" s="11">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" t="s">
+        <v>47</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D41">
+        <v>6</v>
+      </c>
+      <c r="E41" t="s">
+        <v>83</v>
+      </c>
+      <c r="G41">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" t="s">
+        <v>48</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" t="s">
+        <v>49</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D43">
+        <v>6</v>
+      </c>
+      <c r="E43" t="s">
+        <v>83</v>
+      </c>
+      <c r="G43">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" t="s">
+        <v>50</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D44">
+        <v>17</v>
+      </c>
+      <c r="E44" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="10">
         <v>44</v>
       </c>
-      <c r="B20" s="11" t="s">
+      <c r="B45" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="C20" s="11"/>
-      <c r="D20" s="11">
+      <c r="D45" s="10">
         <v>11</v>
       </c>
-      <c r="E20" s="11" t="s">
+      <c r="E45" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="F20" s="11"/>
-      <c r="G20" s="11"/>
-      <c r="H20" s="11"/>
-      <c r="I20" s="11"/>
-      <c r="J20" s="11"/>
-      <c r="K20" s="11"/>
-      <c r="L20" s="11"/>
-      <c r="M20" s="11"/>
-      <c r="N20" s="11"/>
-      <c r="O20" s="11"/>
-      <c r="P20" s="11"/>
-      <c r="Q20" s="11"/>
-      <c r="R20" s="11"/>
-      <c r="S20" s="11"/>
-      <c r="T20" s="11"/>
-      <c r="U20" s="11"/>
-      <c r="V20" s="11"/>
-      <c r="W20" s="11"/>
-      <c r="X20" s="11"/>
-      <c r="Y20" s="11"/>
-      <c r="Z20" s="11"/>
-      <c r="AA20" s="11"/>
-      <c r="AB20" s="11"/>
-      <c r="AC20" s="11"/>
-      <c r="AD20" s="11"/>
-      <c r="AE20" s="11"/>
-    </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>36</v>
-      </c>
-      <c r="B21" t="s">
-        <v>43</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D21">
-        <v>12</v>
-      </c>
-      <c r="E21" t="s">
-        <v>90</v>
-      </c>
-      <c r="G21">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>31</v>
-      </c>
-      <c r="B22" t="s">
-        <v>38</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D22">
-        <v>13</v>
-      </c>
-      <c r="E22" t="s">
-        <v>91</v>
-      </c>
-      <c r="G22">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>38</v>
-      </c>
-      <c r="B23" t="s">
-        <v>45</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D23">
-        <v>13</v>
-      </c>
-      <c r="E23" t="s">
-        <v>91</v>
-      </c>
-      <c r="G23">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>22</v>
-      </c>
-      <c r="B24" t="s">
-        <v>28</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D24">
-        <v>14</v>
-      </c>
-      <c r="E24" t="s">
-        <v>92</v>
-      </c>
-      <c r="G24">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>28</v>
-      </c>
-      <c r="B25" t="s">
-        <v>35</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D25">
-        <v>14</v>
-      </c>
-      <c r="E25" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="26" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A26">
-        <v>13</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D26">
-        <v>15</v>
-      </c>
-      <c r="E26" t="s">
-        <v>93</v>
-      </c>
-      <c r="G26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A27">
-        <v>14</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D27">
-        <v>15</v>
-      </c>
-      <c r="E27" t="s">
-        <v>93</v>
-      </c>
-      <c r="G27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A28">
-        <v>3</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D28">
-        <v>16</v>
-      </c>
-      <c r="E28" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="29" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <v>6</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D29">
-        <v>16</v>
-      </c>
-      <c r="E29" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="30" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <v>43</v>
-      </c>
-      <c r="B30" t="s">
-        <v>50</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D30">
-        <v>17</v>
-      </c>
-      <c r="E30" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="31" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A31">
-        <v>1</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G31">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="32" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A32">
-        <v>2</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G32">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="33" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A33">
-        <v>5</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A34">
-        <v>9</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G34">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="35" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A35">
-        <v>12</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="36" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A36">
-        <v>15</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G36">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A37">
-        <v>17</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="38" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A38">
-        <v>21</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="39" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A39">
-        <v>24</v>
-      </c>
-      <c r="B39" t="s">
-        <v>31</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="40" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A40">
-        <v>29</v>
-      </c>
-      <c r="B40" t="s">
-        <v>36</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="41" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A41">
-        <v>30</v>
-      </c>
-      <c r="B41" t="s">
-        <v>37</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="42" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A42">
-        <v>32</v>
-      </c>
-      <c r="B42" t="s">
-        <v>39</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="G42">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="43" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A43">
-        <v>34</v>
-      </c>
-      <c r="B43" t="s">
-        <v>41</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="44" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A44">
-        <v>35</v>
-      </c>
-      <c r="B44" t="s">
-        <v>42</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="45" spans="1:31" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A45">
-        <v>41</v>
-      </c>
-      <c r="B45" t="s">
-        <v>48</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D45"/>
-      <c r="E45"/>
-      <c r="F45"/>
-      <c r="G45"/>
-      <c r="H45"/>
-      <c r="I45"/>
-      <c r="J45"/>
-      <c r="K45"/>
-      <c r="L45"/>
-      <c r="M45"/>
-      <c r="N45"/>
-      <c r="O45"/>
-      <c r="P45"/>
-      <c r="Q45"/>
-      <c r="R45"/>
-      <c r="S45"/>
-      <c r="T45"/>
-      <c r="U45"/>
-      <c r="V45"/>
-      <c r="W45"/>
-      <c r="X45"/>
-      <c r="Y45"/>
-      <c r="Z45"/>
-      <c r="AA45"/>
-      <c r="AB45"/>
-      <c r="AC45"/>
-      <c r="AD45"/>
-      <c r="AE45"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AE1">
     <sortState ref="A2:AE45">
-      <sortCondition ref="D1"/>
+      <sortCondition ref="A1"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.0249999999999999" bottom="1.0249999999999999" header="0.78749999999999998" footer="0.78749999999999998"/>
@@ -1513,66 +1463,66 @@
     <col min="3" max="3" width="14.109375" customWidth="1"/>
     <col min="4" max="4" width="28" customWidth="1"/>
     <col min="5" max="5" width="39.88671875" customWidth="1"/>
-    <col min="6" max="6" width="14.109375" style="10" customWidth="1"/>
-    <col min="7" max="7" width="14.88671875" style="10" customWidth="1"/>
-    <col min="8" max="8" width="14.5546875" style="10" customWidth="1"/>
-    <col min="9" max="9" width="13.44140625" style="10" customWidth="1"/>
-    <col min="10" max="10" width="13.6640625" style="10" customWidth="1"/>
-    <col min="11" max="11" width="15" style="10" customWidth="1"/>
-    <col min="12" max="12" width="13.6640625" style="10" customWidth="1"/>
-    <col min="13" max="13" width="28.33203125" style="10" customWidth="1"/>
-    <col min="14" max="14" width="20.109375" style="10" customWidth="1"/>
-    <col min="15" max="15" width="17.109375" style="10" customWidth="1"/>
-    <col min="16" max="16" width="23.21875" style="10" customWidth="1"/>
-    <col min="17" max="17" width="20.33203125" style="10" customWidth="1"/>
-    <col min="18" max="18" width="18.109375" style="10" customWidth="1"/>
-    <col min="19" max="19" width="35.6640625" style="10" customWidth="1"/>
-    <col min="20" max="20" width="36.88671875" style="10" customWidth="1"/>
-    <col min="21" max="21" width="17.33203125" style="10" customWidth="1"/>
-    <col min="22" max="22" width="18.21875" style="10" customWidth="1"/>
-    <col min="23" max="23" width="18.33203125" style="10" customWidth="1"/>
-    <col min="24" max="24" width="21.109375" style="10" customWidth="1"/>
-    <col min="25" max="25" width="19.109375" style="10" customWidth="1"/>
-    <col min="26" max="26" width="21.33203125" style="10" customWidth="1"/>
-    <col min="27" max="27" width="19.21875" style="10" customWidth="1"/>
-    <col min="28" max="16384" width="12.6640625" style="10"/>
+    <col min="6" max="6" width="14.109375" style="9" customWidth="1"/>
+    <col min="7" max="7" width="14.88671875" style="9" customWidth="1"/>
+    <col min="8" max="8" width="14.5546875" style="9" customWidth="1"/>
+    <col min="9" max="9" width="13.44140625" style="9" customWidth="1"/>
+    <col min="10" max="10" width="13.6640625" style="9" customWidth="1"/>
+    <col min="11" max="11" width="15" style="9" customWidth="1"/>
+    <col min="12" max="12" width="13.6640625" style="9" customWidth="1"/>
+    <col min="13" max="13" width="28.33203125" style="9" customWidth="1"/>
+    <col min="14" max="14" width="20.109375" style="9" customWidth="1"/>
+    <col min="15" max="15" width="17.109375" style="9" customWidth="1"/>
+    <col min="16" max="16" width="23.21875" style="9" customWidth="1"/>
+    <col min="17" max="17" width="20.33203125" style="9" customWidth="1"/>
+    <col min="18" max="18" width="18.109375" style="9" customWidth="1"/>
+    <col min="19" max="19" width="35.6640625" style="9" customWidth="1"/>
+    <col min="20" max="20" width="36.88671875" style="9" customWidth="1"/>
+    <col min="21" max="21" width="17.33203125" style="9" customWidth="1"/>
+    <col min="22" max="22" width="18.21875" style="9" customWidth="1"/>
+    <col min="23" max="23" width="18.33203125" style="9" customWidth="1"/>
+    <col min="24" max="24" width="21.109375" style="9" customWidth="1"/>
+    <col min="25" max="25" width="19.109375" style="9" customWidth="1"/>
+    <col min="26" max="26" width="21.33203125" style="9" customWidth="1"/>
+    <col min="27" max="27" width="19.21875" style="9" customWidth="1"/>
+    <col min="28" max="16384" width="12.6640625" style="9"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="F1" s="7">
+      <c r="F1" s="6">
         <v>46298</v>
       </c>
-      <c r="G1" s="8">
+      <c r="G1" s="7">
         <v>46312</v>
       </c>
-      <c r="H1" s="8">
+      <c r="H1" s="7">
         <v>46326</v>
       </c>
-      <c r="I1" s="8">
+      <c r="I1" s="7">
         <v>46340</v>
       </c>
-      <c r="J1" s="8">
+      <c r="J1" s="7">
         <v>46354</v>
       </c>
-      <c r="K1" s="8">
+      <c r="K1" s="7">
         <v>46368</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="L1" s="8" t="s">
         <v>77</v>
       </c>
     </row>
@@ -1580,10 +1530,10 @@
       <c r="A2">
         <v>16</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D2">
@@ -1592,7 +1542,7 @@
       <c r="E2" t="s">
         <v>78</v>
       </c>
-      <c r="G2" s="10">
+      <c r="G2" s="9">
         <v>1</v>
       </c>
     </row>
@@ -1600,10 +1550,10 @@
       <c r="A3">
         <v>19</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D3">
@@ -1612,7 +1562,7 @@
       <c r="E3" t="s">
         <v>78</v>
       </c>
-      <c r="G3" s="10">
+      <c r="G3" s="9">
         <v>1</v>
       </c>
     </row>
@@ -1620,10 +1570,10 @@
       <c r="A4">
         <v>18</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D4">
@@ -1632,7 +1582,7 @@
       <c r="E4" t="s">
         <v>79</v>
       </c>
-      <c r="H4" s="10">
+      <c r="H4" s="9">
         <v>1</v>
       </c>
     </row>
@@ -1640,10 +1590,10 @@
       <c r="A5">
         <v>20</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D5">
@@ -1652,7 +1602,7 @@
       <c r="E5" t="s">
         <v>79</v>
       </c>
-      <c r="H5" s="10">
+      <c r="H5" s="9">
         <v>1</v>
       </c>
     </row>
@@ -1660,10 +1610,10 @@
       <c r="A6">
         <v>8</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D6">
@@ -1672,7 +1622,7 @@
       <c r="E6" t="s">
         <v>80</v>
       </c>
-      <c r="H6" s="12">
+      <c r="H6" s="11">
         <v>3</v>
       </c>
     </row>
@@ -1680,10 +1630,10 @@
       <c r="A7">
         <v>10</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D7">
@@ -1692,18 +1642,18 @@
       <c r="E7" t="s">
         <v>80</v>
       </c>
-      <c r="H7" s="12">
+      <c r="H7" s="11">
         <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>11</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D8">
@@ -1712,38 +1662,38 @@
       <c r="E8" t="s">
         <v>81</v>
       </c>
-      <c r="H8" s="10">
+      <c r="H8" s="11">
         <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>25</v>
-      </c>
-      <c r="B9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>29</v>
+        <v>11</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="D9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E9" t="s">
-        <v>82</v>
-      </c>
-      <c r="G9" s="10">
+        <v>81</v>
+      </c>
+      <c r="H9" s="9">
         <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>40</v>
-      </c>
-      <c r="C10" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D10">
@@ -1752,38 +1702,38 @@
       <c r="E10" t="s">
         <v>82</v>
       </c>
-      <c r="G10" s="10">
+      <c r="G10" s="9">
         <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11">
+        <v>33</v>
+      </c>
+      <c r="B11" t="s">
         <v>40</v>
       </c>
-      <c r="B11" t="s">
-        <v>47</v>
-      </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E11" t="s">
-        <v>83</v>
-      </c>
-      <c r="I11" s="10">
-        <v>1</v>
+        <v>82</v>
+      </c>
+      <c r="G11" s="9">
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B12" t="s">
-        <v>49</v>
-      </c>
-      <c r="C12" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D12">
@@ -1792,38 +1742,38 @@
       <c r="E12" t="s">
         <v>83</v>
       </c>
-      <c r="I12" s="10">
+      <c r="I12" s="9">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>4</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>6</v>
+        <v>42</v>
+      </c>
+      <c r="B13" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="D13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E13" t="s">
-        <v>84</v>
-      </c>
-      <c r="I13" s="10">
-        <v>2</v>
+        <v>83</v>
+      </c>
+      <c r="I13" s="9">
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>7</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C14" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D14">
@@ -1832,58 +1782,58 @@
       <c r="E14" t="s">
         <v>84</v>
       </c>
-      <c r="I14" s="10">
+      <c r="I14" s="9">
         <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>37</v>
-      </c>
-      <c r="B15" t="s">
-        <v>44</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>29</v>
+        <v>7</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="D15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E15" t="s">
-        <v>85</v>
-      </c>
-      <c r="I15" s="10">
-        <v>3</v>
+        <v>84</v>
+      </c>
+      <c r="I15" s="9">
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16">
+        <v>37</v>
+      </c>
+      <c r="B16" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D16">
+        <v>8</v>
+      </c>
+      <c r="E16" t="s">
+        <v>85</v>
+      </c>
+      <c r="I16" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17">
         <v>26</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B17" t="s">
         <v>33</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D16">
-        <v>9</v>
-      </c>
-      <c r="E16" t="s">
-        <v>89</v>
-      </c>
-      <c r="I16" s="10">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>27</v>
-      </c>
-      <c r="B17" t="s">
-        <v>34</v>
-      </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D17">
@@ -1892,38 +1842,38 @@
       <c r="E17" t="s">
         <v>89</v>
       </c>
-      <c r="I17" s="10">
+      <c r="I17" s="9">
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18">
+        <v>27</v>
+      </c>
+      <c r="B18" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D18">
+        <v>9</v>
+      </c>
+      <c r="E18" t="s">
+        <v>89</v>
+      </c>
+      <c r="I18" s="9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19">
         <v>23</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B19" t="s">
         <v>30</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D18">
-        <v>10</v>
-      </c>
-      <c r="E18" t="s">
-        <v>86</v>
-      </c>
-      <c r="G18" s="10">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>39</v>
-      </c>
-      <c r="B19" t="s">
-        <v>46</v>
-      </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D19">
@@ -1932,76 +1882,86 @@
       <c r="E19" t="s">
         <v>86</v>
       </c>
-      <c r="G19" s="10">
+      <c r="G19" s="9">
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:10" s="13" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="11">
+    <row r="20" spans="1:11" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>39</v>
+      </c>
+      <c r="B20" t="s">
+        <v>46</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D20">
+        <v>10</v>
+      </c>
+      <c r="E20" t="s">
+        <v>86</v>
+      </c>
+      <c r="F20" s="9"/>
+      <c r="G20" s="9">
+        <v>3</v>
+      </c>
+      <c r="H20" s="9"/>
+      <c r="I20" s="9"/>
+      <c r="J20" s="9"/>
+      <c r="K20" s="9"/>
+    </row>
+    <row r="21" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="10">
         <v>44</v>
       </c>
-      <c r="B20" s="11" t="s">
+      <c r="B21" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="C20" s="11"/>
-      <c r="D20" s="11">
+      <c r="C21" s="10"/>
+      <c r="D21" s="10">
         <v>11</v>
       </c>
-      <c r="E20" s="11" t="s">
+      <c r="E21" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="J20" s="13">
+      <c r="F21" s="12"/>
+      <c r="G21" s="12"/>
+      <c r="H21" s="12"/>
+      <c r="I21" s="12"/>
+      <c r="J21" s="12">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21">
+      <c r="K21" s="12"/>
+    </row>
+    <row r="22" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22">
         <v>36</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B22" t="s">
         <v>43</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D21">
+      <c r="C22" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D22">
         <v>12</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E22" t="s">
         <v>90</v>
       </c>
-      <c r="G21" s="10">
+      <c r="G22" s="9">
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22">
+    <row r="23" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23">
         <v>31</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B23" t="s">
         <v>38</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D22">
-        <v>13</v>
-      </c>
-      <c r="E22" t="s">
-        <v>91</v>
-      </c>
-      <c r="H22" s="10">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>38</v>
-      </c>
-      <c r="B23" t="s">
-        <v>45</v>
-      </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D23">
@@ -2010,38 +1970,38 @@
       <c r="E23" t="s">
         <v>91</v>
       </c>
-      <c r="H23" s="10">
+      <c r="H23" s="9">
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24">
+        <v>38</v>
+      </c>
+      <c r="B24" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D24">
+        <v>13</v>
+      </c>
+      <c r="E24" t="s">
+        <v>91</v>
+      </c>
+      <c r="H24" s="9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25">
         <v>22</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B25" t="s">
         <v>28</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D24">
-        <v>14</v>
-      </c>
-      <c r="E24" t="s">
-        <v>92</v>
-      </c>
-      <c r="I24" s="10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>28</v>
-      </c>
-      <c r="B25" t="s">
-        <v>35</v>
-      </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D25">
@@ -2050,38 +2010,38 @@
       <c r="E25" t="s">
         <v>92</v>
       </c>
-      <c r="I25" s="10">
+      <c r="I25" s="9">
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26">
+        <v>28</v>
+      </c>
+      <c r="B26" t="s">
+        <v>35</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D26">
+        <v>14</v>
+      </c>
+      <c r="E26" t="s">
+        <v>92</v>
+      </c>
+      <c r="I26" s="9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27">
         <v>13</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B27" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C26" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D26">
-        <v>15</v>
-      </c>
-      <c r="E26" t="s">
-        <v>93</v>
-      </c>
-      <c r="H26" s="10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27">
-        <v>14</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C27" s="2" t="s">
+      <c r="C27" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D27">
@@ -2090,38 +2050,38 @@
       <c r="E27" t="s">
         <v>93</v>
       </c>
-      <c r="H27" s="10">
+      <c r="H27" s="9">
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28">
+        <v>14</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D28">
+        <v>15</v>
+      </c>
+      <c r="E28" t="s">
+        <v>93</v>
+      </c>
+      <c r="H28" s="9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29">
         <v>3</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B29" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C28" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D28">
-        <v>16</v>
-      </c>
-      <c r="E28" t="s">
-        <v>94</v>
-      </c>
-      <c r="H28" s="10">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <v>6</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D29">
@@ -2130,71 +2090,80 @@
       <c r="E29" t="s">
         <v>94</v>
       </c>
-      <c r="H29" s="10">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H29" s="9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30">
+        <v>6</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D30">
+        <v>16</v>
+      </c>
+      <c r="E30" t="s">
+        <v>94</v>
+      </c>
+      <c r="H30" s="9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31">
         <v>43</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B31" t="s">
         <v>50</v>
       </c>
-      <c r="C30" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D30">
+      <c r="C31" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D31">
         <v>17</v>
       </c>
-      <c r="E30" t="s">
+      <c r="E31" t="s">
         <v>95</v>
       </c>
-      <c r="I30" s="10">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31">
+      <c r="I31" s="9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32">
         <v>1</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B32" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C31" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32">
-        <v>2</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>5</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>9</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C34" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -2202,10 +2171,10 @@
       <c r="A35">
         <v>12</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B35" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C35" s="1" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2213,10 +2182,10 @@
       <c r="A36">
         <v>15</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B36" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C36" s="1" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2224,10 +2193,10 @@
       <c r="A37">
         <v>17</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="B37" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="C37" s="1" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2235,10 +2204,10 @@
       <c r="A38">
         <v>21</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="B38" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C38" s="1" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2249,7 +2218,7 @@
       <c r="B39" t="s">
         <v>31</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C39" s="1" t="s">
         <v>29</v>
       </c>
     </row>
@@ -2260,7 +2229,7 @@
       <c r="B40" t="s">
         <v>36</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="C40" s="1" t="s">
         <v>29</v>
       </c>
     </row>
@@ -2271,7 +2240,7 @@
       <c r="B41" t="s">
         <v>37</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="C41" s="1" t="s">
         <v>29</v>
       </c>
     </row>
@@ -2282,7 +2251,7 @@
       <c r="B42" t="s">
         <v>39</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="C42" s="1" t="s">
         <v>29</v>
       </c>
     </row>
@@ -2293,7 +2262,7 @@
       <c r="B43" t="s">
         <v>41</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="C43" s="1" t="s">
         <v>29</v>
       </c>
     </row>
@@ -2304,7 +2273,7 @@
       <c r="B44" t="s">
         <v>42</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="C44" s="1" t="s">
         <v>29</v>
       </c>
     </row>
@@ -2315,7 +2284,7 @@
       <c r="B45" t="s">
         <v>48</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="C45" s="1" t="s">
         <v>29</v>
       </c>
     </row>

--- a/2026-2027-IT.xlsx
+++ b/2026-2027-IT.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8196" tabRatio="500" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8196" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="ИТ_5" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="97">
   <si>
     <t>#</t>
   </si>
@@ -312,6 +312,9 @@
   </si>
   <si>
     <t>Redis</t>
+  </si>
+  <si>
+    <t>Йе Йинт Найн</t>
   </si>
 </sst>
 </file>
@@ -439,7 +442,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -464,7 +467,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
@@ -591,7 +593,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AE45"/>
+  <dimension ref="A1:AE46"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.21875" customWidth="1"/>
@@ -704,109 +706,136 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2">
+        <v>16</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>6</v>
+      <c r="E2" t="s">
+        <v>78</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G3">
-        <v>4</v>
+        <v>18</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4">
+        <v>18</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="E4" t="s">
+        <v>79</v>
+      </c>
+      <c r="G4">
         <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4">
-        <v>16</v>
-      </c>
-      <c r="E4" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="D5">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>84</v>
+        <v>79</v>
+      </c>
+      <c r="G5">
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6">
+        <v>3</v>
+      </c>
+      <c r="E6" t="s">
+        <v>80</v>
+      </c>
+      <c r="G6">
         <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D7">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="E7" t="s">
-        <v>94</v>
+        <v>80</v>
+      </c>
+      <c r="G7">
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D8">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E8" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="G8">
         <v>7</v>
@@ -814,634 +843,735 @@
     </row>
     <row r="9" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G9">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>14</v>
+        <v>25</v>
+      </c>
+      <c r="B10" t="s">
+        <v>32</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="D10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G10">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>15</v>
+        <v>33</v>
+      </c>
+      <c r="B11" t="s">
+        <v>40</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="D11">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E11" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G11">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>16</v>
+        <v>40</v>
+      </c>
+      <c r="B12" t="s">
+        <v>47</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="D12">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E12" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G12">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>12</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>17</v>
+        <v>42</v>
+      </c>
+      <c r="B13" t="s">
+        <v>49</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
+      </c>
+      <c r="D13">
+        <v>6</v>
+      </c>
+      <c r="E13" t="s">
+        <v>83</v>
+      </c>
+      <c r="G13">
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="D14">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E14" t="s">
-        <v>93</v>
-      </c>
-      <c r="G14">
-        <v>1</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="D15">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E15" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="G15">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>15</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>21</v>
+        <v>37</v>
+      </c>
+      <c r="B16" t="s">
+        <v>44</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
+      </c>
+      <c r="D16">
+        <v>8</v>
+      </c>
+      <c r="E16" t="s">
+        <v>85</v>
       </c>
       <c r="G16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>16</v>
-      </c>
-      <c r="B17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17">
+        <v>9</v>
+      </c>
+      <c r="E17" t="s">
+        <v>89</v>
+      </c>
+      <c r="G17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>27</v>
+      </c>
+      <c r="B18" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D18">
+        <v>9</v>
+      </c>
+      <c r="E18" t="s">
+        <v>89</v>
+      </c>
+      <c r="G18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>23</v>
+      </c>
+      <c r="B19" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D19">
+        <v>10</v>
+      </c>
+      <c r="E19" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>39</v>
+      </c>
+      <c r="B20" t="s">
+        <v>46</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D20">
+        <v>10</v>
+      </c>
+      <c r="E20" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>44</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D21" s="1">
+        <v>11</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
+      <c r="M21" s="1"/>
+      <c r="N21" s="1"/>
+      <c r="O21" s="1"/>
+      <c r="P21" s="1"/>
+      <c r="Q21" s="1"/>
+      <c r="R21" s="1"/>
+      <c r="S21" s="1"/>
+      <c r="T21" s="1"/>
+      <c r="U21" s="1"/>
+      <c r="V21" s="1"/>
+      <c r="W21" s="1"/>
+      <c r="X21" s="1"/>
+      <c r="Y21" s="1"/>
+      <c r="Z21" s="1"/>
+      <c r="AA21" s="1"/>
+      <c r="AB21" s="1"/>
+      <c r="AC21" s="1"/>
+      <c r="AD21" s="1"/>
+      <c r="AE21" s="1"/>
+    </row>
+    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>45</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D22" s="1">
+        <v>11</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1"/>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1"/>
+      <c r="M22" s="1"/>
+      <c r="N22" s="1"/>
+      <c r="O22" s="1"/>
+      <c r="P22" s="1"/>
+      <c r="Q22" s="1"/>
+      <c r="R22" s="1"/>
+      <c r="S22" s="1"/>
+      <c r="T22" s="1"/>
+      <c r="U22" s="1"/>
+      <c r="V22" s="1"/>
+      <c r="W22" s="1"/>
+      <c r="X22" s="1"/>
+      <c r="Y22" s="1"/>
+      <c r="Z22" s="1"/>
+      <c r="AA22" s="1"/>
+      <c r="AB22" s="1"/>
+      <c r="AC22" s="1"/>
+      <c r="AD22" s="1"/>
+      <c r="AE22" s="1"/>
+    </row>
+    <row r="23" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>36</v>
+      </c>
+      <c r="B23" t="s">
+        <v>43</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D23">
+        <v>12</v>
+      </c>
+      <c r="E23" t="s">
+        <v>90</v>
+      </c>
+      <c r="G23">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>31</v>
+      </c>
+      <c r="B24" t="s">
+        <v>38</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D24">
+        <v>13</v>
+      </c>
+      <c r="E24" t="s">
+        <v>91</v>
+      </c>
+      <c r="G24">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>38</v>
+      </c>
+      <c r="B25" t="s">
+        <v>45</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D25">
+        <v>13</v>
+      </c>
+      <c r="E25" t="s">
+        <v>91</v>
+      </c>
+      <c r="G25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A26">
         <v>22</v>
       </c>
-      <c r="C17" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D17">
-        <v>1</v>
-      </c>
-      <c r="E17" t="s">
-        <v>78</v>
-      </c>
-      <c r="G17">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>17</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>18</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D19">
-        <v>2</v>
-      </c>
-      <c r="E19" t="s">
-        <v>79</v>
-      </c>
-      <c r="G19">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>19</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D20">
-        <v>1</v>
-      </c>
-      <c r="E20" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>20</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D21">
-        <v>2</v>
-      </c>
-      <c r="E21" t="s">
-        <v>79</v>
-      </c>
-      <c r="G21">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>21</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>22</v>
-      </c>
-      <c r="B23" t="s">
+      <c r="B26" t="s">
         <v>28</v>
       </c>
-      <c r="C23" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D23">
+      <c r="C26" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D26">
         <v>14</v>
       </c>
-      <c r="E23" t="s">
+      <c r="E26" t="s">
         <v>92</v>
-      </c>
-      <c r="G23">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>23</v>
-      </c>
-      <c r="B24" t="s">
-        <v>30</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D24">
-        <v>10</v>
-      </c>
-      <c r="E24" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>24</v>
-      </c>
-      <c r="B25" t="s">
-        <v>31</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26">
-        <v>25</v>
-      </c>
-      <c r="B26" t="s">
-        <v>32</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D26">
-        <v>5</v>
-      </c>
-      <c r="E26" t="s">
-        <v>82</v>
       </c>
       <c r="G26">
         <v>8</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D27">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E27" t="s">
-        <v>89</v>
-      </c>
-      <c r="G27">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="28" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>27</v>
-      </c>
-      <c r="B28" t="s">
-        <v>34</v>
+        <v>13</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D28">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E28" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="G28">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>28</v>
-      </c>
-      <c r="B29" t="s">
-        <v>35</v>
+        <v>14</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D29">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E29" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+        <v>93</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>29</v>
-      </c>
-      <c r="B30" t="s">
-        <v>36</v>
+        <v>3</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="D30">
+        <v>16</v>
+      </c>
+      <c r="E30" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="31" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>30</v>
-      </c>
-      <c r="B31" t="s">
-        <v>37</v>
+        <v>6</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>11</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="D31">
+        <v>16</v>
+      </c>
+      <c r="E31" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="32" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="B32" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D32">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E32" t="s">
-        <v>91</v>
-      </c>
-      <c r="G32">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="33" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>1</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33">
-        <v>32</v>
-      </c>
-      <c r="B33" t="s">
-        <v>39</v>
-      </c>
       <c r="C33" s="1" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="G33">
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>33</v>
-      </c>
-      <c r="B34" t="s">
-        <v>40</v>
+        <v>2</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D34">
+        <v>6</v>
+      </c>
+      <c r="G34">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A35">
         <v>5</v>
       </c>
-      <c r="E34" t="s">
-        <v>82</v>
-      </c>
-      <c r="G34">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35">
+      <c r="B35" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>12</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="37" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>15</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>17</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="39" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>21</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="40" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>24</v>
+      </c>
+      <c r="B40" t="s">
+        <v>31</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="41" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>29</v>
+      </c>
+      <c r="B41" t="s">
+        <v>36</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="42" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>30</v>
+      </c>
+      <c r="B42" t="s">
+        <v>37</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="43" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>32</v>
+      </c>
+      <c r="B43" t="s">
+        <v>39</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G43">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A44">
         <v>34</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B44" t="s">
         <v>41</v>
       </c>
-      <c r="C35" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36">
+      <c r="C44" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="45" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45">
         <v>35</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B45" t="s">
         <v>42</v>
       </c>
-      <c r="C36" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37">
-        <v>36</v>
-      </c>
-      <c r="B37" t="s">
-        <v>43</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D37">
-        <v>12</v>
-      </c>
-      <c r="E37" t="s">
-        <v>90</v>
-      </c>
-      <c r="G37">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38">
-        <v>37</v>
-      </c>
-      <c r="B38" t="s">
-        <v>44</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D38">
-        <v>8</v>
-      </c>
-      <c r="E38" t="s">
-        <v>85</v>
-      </c>
-      <c r="G38">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39">
-        <v>38</v>
-      </c>
-      <c r="B39" t="s">
-        <v>45</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D39">
-        <v>13</v>
-      </c>
-      <c r="E39" t="s">
-        <v>91</v>
-      </c>
-      <c r="G39">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40">
-        <v>39</v>
-      </c>
-      <c r="B40" t="s">
-        <v>46</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D40">
-        <v>10</v>
-      </c>
-      <c r="E40" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41">
-        <v>40</v>
-      </c>
-      <c r="B41" t="s">
-        <v>47</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D41">
-        <v>6</v>
-      </c>
-      <c r="E41" t="s">
-        <v>83</v>
-      </c>
-      <c r="G41">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42">
+      <c r="C45" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D45"/>
+      <c r="E45"/>
+      <c r="F45"/>
+      <c r="G45"/>
+      <c r="H45"/>
+      <c r="I45"/>
+      <c r="J45"/>
+      <c r="K45"/>
+      <c r="L45"/>
+      <c r="M45"/>
+      <c r="N45"/>
+      <c r="O45"/>
+      <c r="P45"/>
+      <c r="Q45"/>
+      <c r="R45"/>
+      <c r="S45"/>
+      <c r="T45"/>
+      <c r="U45"/>
+      <c r="V45"/>
+      <c r="W45"/>
+      <c r="X45"/>
+      <c r="Y45"/>
+      <c r="Z45"/>
+      <c r="AA45"/>
+      <c r="AB45"/>
+      <c r="AC45"/>
+      <c r="AD45"/>
+      <c r="AE45"/>
+    </row>
+    <row r="46" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46">
         <v>41</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B46" t="s">
         <v>48</v>
       </c>
-      <c r="C42" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43">
-        <v>42</v>
-      </c>
-      <c r="B43" t="s">
-        <v>49</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D43">
-        <v>6</v>
-      </c>
-      <c r="E43" t="s">
-        <v>83</v>
-      </c>
-      <c r="G43">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44">
-        <v>43</v>
-      </c>
-      <c r="B44" t="s">
-        <v>50</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D44">
-        <v>17</v>
-      </c>
-      <c r="E44" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="10">
-        <v>44</v>
-      </c>
-      <c r="B45" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="D45" s="10">
-        <v>11</v>
-      </c>
-      <c r="E45" s="10" t="s">
-        <v>88</v>
-      </c>
+      <c r="C46" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D46"/>
+      <c r="E46"/>
+      <c r="F46"/>
+      <c r="G46"/>
+      <c r="H46"/>
+      <c r="I46"/>
+      <c r="J46"/>
+      <c r="K46"/>
+      <c r="L46"/>
+      <c r="M46"/>
+      <c r="N46"/>
+      <c r="O46"/>
+      <c r="P46"/>
+      <c r="Q46"/>
+      <c r="R46"/>
+      <c r="S46"/>
+      <c r="T46"/>
+      <c r="U46"/>
+      <c r="V46"/>
+      <c r="W46"/>
+      <c r="X46"/>
+      <c r="Y46"/>
+      <c r="Z46"/>
+      <c r="AA46"/>
+      <c r="AB46"/>
+      <c r="AC46"/>
+      <c r="AD46"/>
+      <c r="AE46"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AE1">
-    <sortState ref="A2:AE45">
-      <sortCondition ref="A1"/>
+    <sortState ref="A2:AE46">
+      <sortCondition ref="D1"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.0249999999999999" bottom="1.0249999999999999" header="0.78749999999999998" footer="0.78749999999999998"/>
@@ -1455,7 +1585,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L45"/>
+  <dimension ref="A1:L46"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.21875" customWidth="1"/>
@@ -1622,7 +1752,7 @@
       <c r="E6" t="s">
         <v>80</v>
       </c>
-      <c r="H6" s="11">
+      <c r="H6" s="10">
         <v>3</v>
       </c>
     </row>
@@ -1642,7 +1772,7 @@
       <c r="E7" t="s">
         <v>80</v>
       </c>
-      <c r="H7" s="11">
+      <c r="H7" s="10">
         <v>3</v>
       </c>
     </row>
@@ -1662,7 +1792,7 @@
       <c r="E8" t="s">
         <v>81</v>
       </c>
-      <c r="H8" s="11">
+      <c r="H8" s="10">
         <v>2</v>
       </c>
     </row>
@@ -1886,7 +2016,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:11" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" s="11" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>39</v>
       </c>
@@ -1912,74 +2042,72 @@
       <c r="K20" s="9"/>
     </row>
     <row r="21" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="10">
+      <c r="A21" s="1">
         <v>44</v>
       </c>
-      <c r="B21" s="10" t="s">
+      <c r="B21" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="C21" s="10"/>
-      <c r="D21" s="10">
+      <c r="C21" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D21" s="1">
         <v>11</v>
       </c>
-      <c r="E21" s="10" t="s">
+      <c r="E21" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="F21" s="12"/>
-      <c r="G21" s="12"/>
-      <c r="H21" s="12"/>
-      <c r="I21" s="12"/>
-      <c r="J21" s="12">
+      <c r="J21" s="9">
         <v>1</v>
       </c>
-      <c r="K21" s="12"/>
     </row>
     <row r="22" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>36</v>
-      </c>
-      <c r="B22" t="s">
-        <v>43</v>
+      <c r="A22" s="1">
+        <v>45</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>96</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D22">
-        <v>12</v>
-      </c>
-      <c r="E22" t="s">
-        <v>90</v>
-      </c>
-      <c r="G22" s="9">
-        <v>4</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="D22" s="1">
+        <v>11</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="J22" s="9">
+        <v>1</v>
+      </c>
+      <c r="K22" s="1"/>
     </row>
     <row r="23" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="B23" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D23">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E23" t="s">
-        <v>91</v>
-      </c>
-      <c r="H23" s="9">
+        <v>90</v>
+      </c>
+      <c r="G23" s="9">
         <v>4</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24">
+        <v>31</v>
+      </c>
+      <c r="B24" t="s">
         <v>38</v>
-      </c>
-      <c r="B24" t="s">
-        <v>45</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>29</v>
@@ -1996,30 +2124,30 @@
     </row>
     <row r="25" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="B25" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D25">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E25" t="s">
-        <v>92</v>
-      </c>
-      <c r="I25" s="9">
-        <v>5</v>
+        <v>91</v>
+      </c>
+      <c r="H25" s="9">
+        <v>4</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26">
+        <v>22</v>
+      </c>
+      <c r="B26" t="s">
         <v>28</v>
-      </c>
-      <c r="B26" t="s">
-        <v>35</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>29</v>
@@ -2036,30 +2164,30 @@
     </row>
     <row r="27" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>13</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>19</v>
+        <v>28</v>
+      </c>
+      <c r="B27" t="s">
+        <v>35</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D27">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E27" t="s">
-        <v>93</v>
-      </c>
-      <c r="H27" s="9">
+        <v>92</v>
+      </c>
+      <c r="I27" s="9">
         <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>18</v>
@@ -2076,30 +2204,30 @@
     </row>
     <row r="29" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="D29">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E29" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H29" s="9">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>6</v>
@@ -2116,181 +2244,209 @@
     </row>
     <row r="31" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>43</v>
-      </c>
-      <c r="B31" t="s">
-        <v>50</v>
+        <v>6</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>11</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="D31">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E31" t="s">
-        <v>95</v>
-      </c>
-      <c r="I31" s="9">
+        <v>94</v>
+      </c>
+      <c r="H31" s="9">
         <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32">
+        <v>43</v>
+      </c>
+      <c r="B32" t="s">
+        <v>50</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D32">
+        <v>17</v>
+      </c>
+      <c r="E32" t="s">
+        <v>95</v>
+      </c>
+      <c r="I32" s="9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33">
         <v>1</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B33" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C32" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33">
+      <c r="C33" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34">
         <v>2</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B34" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C33" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34">
+      <c r="C34" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35">
         <v>5</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B35" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C34" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35">
+      <c r="C35" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36">
         <v>12</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="B36" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36">
-        <v>15</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>21</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39">
+        <v>21</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40">
         <v>24</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B40" t="s">
         <v>31</v>
       </c>
-      <c r="C39" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40">
-        <v>29</v>
-      </c>
-      <c r="B40" t="s">
+      <c r="C40" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>29</v>
+      </c>
+      <c r="B41" t="s">
         <v>36</v>
       </c>
-      <c r="C40" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41">
+      <c r="C41" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42">
         <v>30</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B42" t="s">
         <v>37</v>
       </c>
-      <c r="C41" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42">
+      <c r="C42" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43">
         <v>32</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B43" t="s">
         <v>39</v>
       </c>
-      <c r="C42" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43">
+      <c r="C43" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44">
         <v>34</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B44" t="s">
         <v>41</v>
       </c>
-      <c r="C43" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44">
+      <c r="C44" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45">
         <v>35</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B45" t="s">
         <v>42</v>
       </c>
-      <c r="C44" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45">
+      <c r="C45" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" s="1" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A46">
         <v>41</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B46" t="s">
         <v>48</v>
       </c>
-      <c r="C45" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="C46" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D46"/>
+      <c r="E46"/>
+      <c r="F46" s="9"/>
+      <c r="G46" s="9"/>
+      <c r="H46" s="9"/>
+      <c r="I46" s="9"/>
+      <c r="J46" s="9"/>
+      <c r="K46" s="9"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:K1">
-    <sortState ref="A2:K45">
+    <sortState ref="A2:K46">
       <sortCondition ref="D1"/>
     </sortState>
   </autoFilter>

--- a/2026-2027-IT.xlsx
+++ b/2026-2027-IT.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="98">
   <si>
     <t>#</t>
   </si>
@@ -315,6 +315,9 @@
   </si>
   <si>
     <t>Йе Йинт Найн</t>
+  </si>
+  <si>
+    <t>+</t>
   </si>
 </sst>
 </file>
@@ -442,7 +445,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -469,6 +472,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -603,10 +612,11 @@
     <col min="5" max="5" width="39.88671875" customWidth="1"/>
     <col min="6" max="6" width="22.44140625" customWidth="1"/>
     <col min="7" max="7" width="22.88671875" customWidth="1"/>
-    <col min="8" max="18" width="22.44140625" customWidth="1"/>
-    <col min="19" max="19" width="33.21875" customWidth="1"/>
-    <col min="20" max="20" width="28.6640625" customWidth="1"/>
-    <col min="21" max="31" width="22.44140625" customWidth="1"/>
+    <col min="8" max="8" width="22.44140625" customWidth="1"/>
+    <col min="9" max="18" width="22.44140625" style="12" customWidth="1"/>
+    <col min="19" max="19" width="33.21875" style="12" customWidth="1"/>
+    <col min="20" max="20" width="28.6640625" style="12" customWidth="1"/>
+    <col min="21" max="31" width="22.44140625" style="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:31" ht="29.4" customHeight="1" x14ac:dyDescent="0.25">
@@ -1091,29 +1101,29 @@
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
-      <c r="J21" s="1"/>
-      <c r="K21" s="1"/>
-      <c r="L21" s="1"/>
-      <c r="M21" s="1"/>
-      <c r="N21" s="1"/>
-      <c r="O21" s="1"/>
-      <c r="P21" s="1"/>
-      <c r="Q21" s="1"/>
-      <c r="R21" s="1"/>
-      <c r="S21" s="1"/>
-      <c r="T21" s="1"/>
-      <c r="U21" s="1"/>
-      <c r="V21" s="1"/>
-      <c r="W21" s="1"/>
-      <c r="X21" s="1"/>
-      <c r="Y21" s="1"/>
-      <c r="Z21" s="1"/>
-      <c r="AA21" s="1"/>
-      <c r="AB21" s="1"/>
-      <c r="AC21" s="1"/>
-      <c r="AD21" s="1"/>
-      <c r="AE21" s="1"/>
+      <c r="I21" s="13"/>
+      <c r="J21" s="13"/>
+      <c r="K21" s="13"/>
+      <c r="L21" s="13"/>
+      <c r="M21" s="13"/>
+      <c r="N21" s="13"/>
+      <c r="O21" s="13"/>
+      <c r="P21" s="13"/>
+      <c r="Q21" s="13"/>
+      <c r="R21" s="13"/>
+      <c r="S21" s="13"/>
+      <c r="T21" s="13"/>
+      <c r="U21" s="13"/>
+      <c r="V21" s="13"/>
+      <c r="W21" s="13"/>
+      <c r="X21" s="13"/>
+      <c r="Y21" s="13"/>
+      <c r="Z21" s="13"/>
+      <c r="AA21" s="13"/>
+      <c r="AB21" s="13"/>
+      <c r="AC21" s="13"/>
+      <c r="AD21" s="13"/>
+      <c r="AE21" s="13"/>
     </row>
     <row r="22" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
@@ -1134,29 +1144,29 @@
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
-      <c r="J22" s="1"/>
-      <c r="K22" s="1"/>
-      <c r="L22" s="1"/>
-      <c r="M22" s="1"/>
-      <c r="N22" s="1"/>
-      <c r="O22" s="1"/>
-      <c r="P22" s="1"/>
-      <c r="Q22" s="1"/>
-      <c r="R22" s="1"/>
-      <c r="S22" s="1"/>
-      <c r="T22" s="1"/>
-      <c r="U22" s="1"/>
-      <c r="V22" s="1"/>
-      <c r="W22" s="1"/>
-      <c r="X22" s="1"/>
-      <c r="Y22" s="1"/>
-      <c r="Z22" s="1"/>
-      <c r="AA22" s="1"/>
-      <c r="AB22" s="1"/>
-      <c r="AC22" s="1"/>
-      <c r="AD22" s="1"/>
-      <c r="AE22" s="1"/>
+      <c r="I22" s="13"/>
+      <c r="J22" s="13"/>
+      <c r="K22" s="13"/>
+      <c r="L22" s="13"/>
+      <c r="M22" s="13"/>
+      <c r="N22" s="13"/>
+      <c r="O22" s="13"/>
+      <c r="P22" s="13"/>
+      <c r="Q22" s="13"/>
+      <c r="R22" s="13"/>
+      <c r="S22" s="13"/>
+      <c r="T22" s="13"/>
+      <c r="U22" s="13"/>
+      <c r="V22" s="13"/>
+      <c r="W22" s="13"/>
+      <c r="X22" s="13"/>
+      <c r="Y22" s="13"/>
+      <c r="Z22" s="13"/>
+      <c r="AA22" s="13"/>
+      <c r="AB22" s="13"/>
+      <c r="AC22" s="13"/>
+      <c r="AD22" s="13"/>
+      <c r="AE22" s="13"/>
     </row>
     <row r="23" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A23">
@@ -1236,6 +1246,9 @@
       </c>
       <c r="G26">
         <v>8</v>
+      </c>
+      <c r="AD26" s="12" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="27" spans="1:31" x14ac:dyDescent="0.25">
@@ -1505,29 +1518,29 @@
       <c r="F45"/>
       <c r="G45"/>
       <c r="H45"/>
-      <c r="I45"/>
-      <c r="J45"/>
-      <c r="K45"/>
-      <c r="L45"/>
-      <c r="M45"/>
-      <c r="N45"/>
-      <c r="O45"/>
-      <c r="P45"/>
-      <c r="Q45"/>
-      <c r="R45"/>
-      <c r="S45"/>
-      <c r="T45"/>
-      <c r="U45"/>
-      <c r="V45"/>
-      <c r="W45"/>
-      <c r="X45"/>
-      <c r="Y45"/>
-      <c r="Z45"/>
-      <c r="AA45"/>
-      <c r="AB45"/>
-      <c r="AC45"/>
-      <c r="AD45"/>
-      <c r="AE45"/>
+      <c r="I45" s="12"/>
+      <c r="J45" s="12"/>
+      <c r="K45" s="12"/>
+      <c r="L45" s="12"/>
+      <c r="M45" s="12"/>
+      <c r="N45" s="12"/>
+      <c r="O45" s="12"/>
+      <c r="P45" s="12"/>
+      <c r="Q45" s="12"/>
+      <c r="R45" s="12"/>
+      <c r="S45" s="12"/>
+      <c r="T45" s="12"/>
+      <c r="U45" s="12"/>
+      <c r="V45" s="12"/>
+      <c r="W45" s="12"/>
+      <c r="X45" s="12"/>
+      <c r="Y45" s="12"/>
+      <c r="Z45" s="12"/>
+      <c r="AA45" s="12"/>
+      <c r="AB45" s="12"/>
+      <c r="AC45" s="12"/>
+      <c r="AD45" s="12"/>
+      <c r="AE45" s="12"/>
     </row>
     <row r="46" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46">
@@ -1544,29 +1557,29 @@
       <c r="F46"/>
       <c r="G46"/>
       <c r="H46"/>
-      <c r="I46"/>
-      <c r="J46"/>
-      <c r="K46"/>
-      <c r="L46"/>
-      <c r="M46"/>
-      <c r="N46"/>
-      <c r="O46"/>
-      <c r="P46"/>
-      <c r="Q46"/>
-      <c r="R46"/>
-      <c r="S46"/>
-      <c r="T46"/>
-      <c r="U46"/>
-      <c r="V46"/>
-      <c r="W46"/>
-      <c r="X46"/>
-      <c r="Y46"/>
-      <c r="Z46"/>
-      <c r="AA46"/>
-      <c r="AB46"/>
-      <c r="AC46"/>
-      <c r="AD46"/>
-      <c r="AE46"/>
+      <c r="I46" s="12"/>
+      <c r="J46" s="12"/>
+      <c r="K46" s="12"/>
+      <c r="L46" s="12"/>
+      <c r="M46" s="12"/>
+      <c r="N46" s="12"/>
+      <c r="O46" s="12"/>
+      <c r="P46" s="12"/>
+      <c r="Q46" s="12"/>
+      <c r="R46" s="12"/>
+      <c r="S46" s="12"/>
+      <c r="T46" s="12"/>
+      <c r="U46" s="12"/>
+      <c r="V46" s="12"/>
+      <c r="W46" s="12"/>
+      <c r="X46" s="12"/>
+      <c r="Y46" s="12"/>
+      <c r="Z46" s="12"/>
+      <c r="AA46" s="12"/>
+      <c r="AB46" s="12"/>
+      <c r="AC46" s="12"/>
+      <c r="AD46" s="12"/>
+      <c r="AE46" s="12"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AE1">

--- a/2026-2027-IT.xlsx
+++ b/2026-2027-IT.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8196" tabRatio="500"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8196" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="ИТ_5" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="100">
   <si>
     <t>#</t>
   </si>
@@ -318,6 +318,12 @@
   </si>
   <si>
     <t>+</t>
+  </si>
+  <si>
+    <t>Дорошенко</t>
+  </si>
+  <si>
+    <t>Технология WebAssembly</t>
   </si>
 </sst>
 </file>
@@ -445,7 +451,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -470,12 +476,18 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -602,7 +614,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AE46"/>
+  <dimension ref="A1:AE47"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.21875" customWidth="1"/>
@@ -613,10 +625,10 @@
     <col min="6" max="6" width="22.44140625" customWidth="1"/>
     <col min="7" max="7" width="22.88671875" customWidth="1"/>
     <col min="8" max="8" width="22.44140625" customWidth="1"/>
-    <col min="9" max="18" width="22.44140625" style="12" customWidth="1"/>
-    <col min="19" max="19" width="33.21875" style="12" customWidth="1"/>
-    <col min="20" max="20" width="28.6640625" style="12" customWidth="1"/>
-    <col min="21" max="31" width="22.44140625" style="12" customWidth="1"/>
+    <col min="9" max="18" width="22.44140625" style="11" customWidth="1"/>
+    <col min="19" max="19" width="33.21875" style="11" customWidth="1"/>
+    <col min="20" max="20" width="28.6640625" style="11" customWidth="1"/>
+    <col min="21" max="31" width="22.44140625" style="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:31" ht="29.4" customHeight="1" x14ac:dyDescent="0.25">
@@ -1083,90 +1095,90 @@
       </c>
     </row>
     <row r="21" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A21" s="1">
+      <c r="A21" s="13">
         <v>44</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="C21" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D21" s="1">
+      <c r="C21" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="D21" s="13">
         <v>11</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="E21" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="13"/>
-      <c r="J21" s="13"/>
-      <c r="K21" s="13"/>
-      <c r="L21" s="13"/>
-      <c r="M21" s="13"/>
-      <c r="N21" s="13"/>
-      <c r="O21" s="13"/>
-      <c r="P21" s="13"/>
-      <c r="Q21" s="13"/>
-      <c r="R21" s="13"/>
-      <c r="S21" s="13"/>
-      <c r="T21" s="13"/>
-      <c r="U21" s="13"/>
-      <c r="V21" s="13"/>
-      <c r="W21" s="13"/>
-      <c r="X21" s="13"/>
-      <c r="Y21" s="13"/>
-      <c r="Z21" s="13"/>
-      <c r="AA21" s="13"/>
-      <c r="AB21" s="13"/>
-      <c r="AC21" s="13"/>
-      <c r="AD21" s="13"/>
-      <c r="AE21" s="13"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="13"/>
+      <c r="I21" s="14"/>
+      <c r="J21" s="14"/>
+      <c r="K21" s="14"/>
+      <c r="L21" s="14"/>
+      <c r="M21" s="14"/>
+      <c r="N21" s="14"/>
+      <c r="O21" s="14"/>
+      <c r="P21" s="14"/>
+      <c r="Q21" s="14"/>
+      <c r="R21" s="14"/>
+      <c r="S21" s="14"/>
+      <c r="T21" s="14"/>
+      <c r="U21" s="14"/>
+      <c r="V21" s="14"/>
+      <c r="W21" s="14"/>
+      <c r="X21" s="14"/>
+      <c r="Y21" s="14"/>
+      <c r="Z21" s="14"/>
+      <c r="AA21" s="14"/>
+      <c r="AB21" s="14"/>
+      <c r="AC21" s="14"/>
+      <c r="AD21" s="14"/>
+      <c r="AE21" s="14"/>
     </row>
     <row r="22" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A22" s="1">
+      <c r="A22" s="13">
         <v>45</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D22" s="1">
+      <c r="C22" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="D22" s="13">
         <v>11</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="E22" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
-      <c r="I22" s="13"/>
-      <c r="J22" s="13"/>
-      <c r="K22" s="13"/>
-      <c r="L22" s="13"/>
-      <c r="M22" s="13"/>
-      <c r="N22" s="13"/>
-      <c r="O22" s="13"/>
-      <c r="P22" s="13"/>
-      <c r="Q22" s="13"/>
-      <c r="R22" s="13"/>
-      <c r="S22" s="13"/>
-      <c r="T22" s="13"/>
-      <c r="U22" s="13"/>
-      <c r="V22" s="13"/>
-      <c r="W22" s="13"/>
-      <c r="X22" s="13"/>
-      <c r="Y22" s="13"/>
-      <c r="Z22" s="13"/>
-      <c r="AA22" s="13"/>
-      <c r="AB22" s="13"/>
-      <c r="AC22" s="13"/>
-      <c r="AD22" s="13"/>
-      <c r="AE22" s="13"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="13"/>
+      <c r="H22" s="13"/>
+      <c r="I22" s="14"/>
+      <c r="J22" s="14"/>
+      <c r="K22" s="14"/>
+      <c r="L22" s="14"/>
+      <c r="M22" s="14"/>
+      <c r="N22" s="14"/>
+      <c r="O22" s="14"/>
+      <c r="P22" s="14"/>
+      <c r="Q22" s="14"/>
+      <c r="R22" s="14"/>
+      <c r="S22" s="14"/>
+      <c r="T22" s="14"/>
+      <c r="U22" s="14"/>
+      <c r="V22" s="14"/>
+      <c r="W22" s="14"/>
+      <c r="X22" s="14"/>
+      <c r="Y22" s="14"/>
+      <c r="Z22" s="14"/>
+      <c r="AA22" s="14"/>
+      <c r="AB22" s="14"/>
+      <c r="AC22" s="14"/>
+      <c r="AD22" s="14"/>
+      <c r="AE22" s="14"/>
     </row>
     <row r="23" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A23">
@@ -1247,7 +1259,7 @@
       <c r="G26">
         <v>8</v>
       </c>
-      <c r="AD26" s="12" t="s">
+      <c r="AD26" s="11" t="s">
         <v>97</v>
       </c>
     </row>
@@ -1360,25 +1372,52 @@
       </c>
     </row>
     <row r="33" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A33">
-        <v>1</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G33">
-        <v>4</v>
-      </c>
+      <c r="A33" s="13">
+        <v>46</v>
+      </c>
+      <c r="B33" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="C33" s="13"/>
+      <c r="D33" s="13">
+        <v>18</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="F33" s="13"/>
+      <c r="G33" s="13"/>
+      <c r="H33" s="13"/>
+      <c r="I33" s="14"/>
+      <c r="J33" s="14"/>
+      <c r="K33" s="14"/>
+      <c r="L33" s="14"/>
+      <c r="M33" s="14"/>
+      <c r="N33" s="14"/>
+      <c r="O33" s="14"/>
+      <c r="P33" s="14"/>
+      <c r="Q33" s="14"/>
+      <c r="R33" s="14"/>
+      <c r="S33" s="14"/>
+      <c r="T33" s="14"/>
+      <c r="U33" s="14"/>
+      <c r="V33" s="14"/>
+      <c r="W33" s="14"/>
+      <c r="X33" s="14"/>
+      <c r="Y33" s="14"/>
+      <c r="Z33" s="14"/>
+      <c r="AA33" s="14"/>
+      <c r="AB33" s="14"/>
+      <c r="AC33" s="14"/>
+      <c r="AD33" s="14"/>
+      <c r="AE33" s="14"/>
     </row>
     <row r="34" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>6</v>
@@ -1389,57 +1428,60 @@
     </row>
     <row r="35" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>6</v>
+      </c>
+      <c r="G35">
+        <v>4</v>
       </c>
     </row>
     <row r="36" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G37">
-        <v>1</v>
-      </c>
     </row>
     <row r="38" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="G38">
+        <v>1</v>
+      </c>
     </row>
     <row r="39" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>18</v>
@@ -1447,21 +1489,21 @@
     </row>
     <row r="40" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>24</v>
-      </c>
-      <c r="B40" t="s">
-        <v>31</v>
+        <v>21</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
     </row>
     <row r="41" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B41" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>29</v>
@@ -1469,10 +1511,10 @@
     </row>
     <row r="42" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B42" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>29</v>
@@ -1480,35 +1522,35 @@
     </row>
     <row r="43" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B43" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="G43">
-        <v>4</v>
       </c>
     </row>
     <row r="44" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A44">
+        <v>32</v>
+      </c>
+      <c r="B44" t="s">
+        <v>39</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G44">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:31" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45">
         <v>34</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B45" t="s">
         <v>41</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="45" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A45">
-        <v>35</v>
-      </c>
-      <c r="B45" t="s">
-        <v>42</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>29</v>
@@ -1518,36 +1560,36 @@
       <c r="F45"/>
       <c r="G45"/>
       <c r="H45"/>
-      <c r="I45" s="12"/>
-      <c r="J45" s="12"/>
-      <c r="K45" s="12"/>
-      <c r="L45" s="12"/>
-      <c r="M45" s="12"/>
-      <c r="N45" s="12"/>
-      <c r="O45" s="12"/>
-      <c r="P45" s="12"/>
-      <c r="Q45" s="12"/>
-      <c r="R45" s="12"/>
-      <c r="S45" s="12"/>
-      <c r="T45" s="12"/>
-      <c r="U45" s="12"/>
-      <c r="V45" s="12"/>
-      <c r="W45" s="12"/>
-      <c r="X45" s="12"/>
-      <c r="Y45" s="12"/>
-      <c r="Z45" s="12"/>
-      <c r="AA45" s="12"/>
-      <c r="AB45" s="12"/>
-      <c r="AC45" s="12"/>
-      <c r="AD45" s="12"/>
-      <c r="AE45" s="12"/>
-    </row>
-    <row r="46" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I45" s="11"/>
+      <c r="J45" s="11"/>
+      <c r="K45" s="11"/>
+      <c r="L45" s="11"/>
+      <c r="M45" s="11"/>
+      <c r="N45" s="11"/>
+      <c r="O45" s="11"/>
+      <c r="P45" s="11"/>
+      <c r="Q45" s="11"/>
+      <c r="R45" s="11"/>
+      <c r="S45" s="11"/>
+      <c r="T45" s="11"/>
+      <c r="U45" s="11"/>
+      <c r="V45" s="11"/>
+      <c r="W45" s="11"/>
+      <c r="X45" s="11"/>
+      <c r="Y45" s="11"/>
+      <c r="Z45" s="11"/>
+      <c r="AA45" s="11"/>
+      <c r="AB45" s="11"/>
+      <c r="AC45" s="11"/>
+      <c r="AD45" s="11"/>
+      <c r="AE45" s="11"/>
+    </row>
+    <row r="46" spans="1:31" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B46" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>29</v>
@@ -1557,33 +1599,72 @@
       <c r="F46"/>
       <c r="G46"/>
       <c r="H46"/>
-      <c r="I46" s="12"/>
-      <c r="J46" s="12"/>
-      <c r="K46" s="12"/>
-      <c r="L46" s="12"/>
-      <c r="M46" s="12"/>
-      <c r="N46" s="12"/>
-      <c r="O46" s="12"/>
-      <c r="P46" s="12"/>
-      <c r="Q46" s="12"/>
-      <c r="R46" s="12"/>
-      <c r="S46" s="12"/>
-      <c r="T46" s="12"/>
-      <c r="U46" s="12"/>
-      <c r="V46" s="12"/>
-      <c r="W46" s="12"/>
-      <c r="X46" s="12"/>
-      <c r="Y46" s="12"/>
-      <c r="Z46" s="12"/>
-      <c r="AA46" s="12"/>
-      <c r="AB46" s="12"/>
-      <c r="AC46" s="12"/>
-      <c r="AD46" s="12"/>
-      <c r="AE46" s="12"/>
+      <c r="I46" s="11"/>
+      <c r="J46" s="11"/>
+      <c r="K46" s="11"/>
+      <c r="L46" s="11"/>
+      <c r="M46" s="11"/>
+      <c r="N46" s="11"/>
+      <c r="O46" s="11"/>
+      <c r="P46" s="11"/>
+      <c r="Q46" s="11"/>
+      <c r="R46" s="11"/>
+      <c r="S46" s="11"/>
+      <c r="T46" s="11"/>
+      <c r="U46" s="11"/>
+      <c r="V46" s="11"/>
+      <c r="W46" s="11"/>
+      <c r="X46" s="11"/>
+      <c r="Y46" s="11"/>
+      <c r="Z46" s="11"/>
+      <c r="AA46" s="11"/>
+      <c r="AB46" s="11"/>
+      <c r="AC46" s="11"/>
+      <c r="AD46" s="11"/>
+      <c r="AE46" s="11"/>
+    </row>
+    <row r="47" spans="1:31" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>41</v>
+      </c>
+      <c r="B47" t="s">
+        <v>48</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D47"/>
+      <c r="E47"/>
+      <c r="F47"/>
+      <c r="G47"/>
+      <c r="H47"/>
+      <c r="I47" s="11"/>
+      <c r="J47" s="11"/>
+      <c r="K47" s="11"/>
+      <c r="L47" s="11"/>
+      <c r="M47" s="11"/>
+      <c r="N47" s="11"/>
+      <c r="O47" s="11"/>
+      <c r="P47" s="11"/>
+      <c r="Q47" s="11"/>
+      <c r="R47" s="11"/>
+      <c r="S47" s="11"/>
+      <c r="T47" s="11"/>
+      <c r="U47" s="11"/>
+      <c r="V47" s="11"/>
+      <c r="W47" s="11"/>
+      <c r="X47" s="11"/>
+      <c r="Y47" s="11"/>
+      <c r="Z47" s="11"/>
+      <c r="AA47" s="11"/>
+      <c r="AB47" s="11"/>
+      <c r="AC47" s="11"/>
+      <c r="AD47" s="11"/>
+      <c r="AE47" s="11"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AE1">
-    <sortState ref="A2:AE46">
+    <sortState ref="A2:AE47">
       <sortCondition ref="D1"/>
     </sortState>
   </autoFilter>
@@ -1598,7 +1679,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L46"/>
+  <dimension ref="A1:AE47"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.21875" customWidth="1"/>
@@ -1606,13 +1687,13 @@
     <col min="3" max="3" width="14.109375" customWidth="1"/>
     <col min="4" max="4" width="28" customWidth="1"/>
     <col min="5" max="5" width="39.88671875" customWidth="1"/>
-    <col min="6" max="6" width="14.109375" style="9" customWidth="1"/>
-    <col min="7" max="7" width="14.88671875" style="9" customWidth="1"/>
-    <col min="8" max="8" width="14.5546875" style="9" customWidth="1"/>
-    <col min="9" max="9" width="13.44140625" style="9" customWidth="1"/>
-    <col min="10" max="10" width="13.6640625" style="9" customWidth="1"/>
-    <col min="11" max="11" width="15" style="9" customWidth="1"/>
-    <col min="12" max="12" width="13.6640625" style="9" customWidth="1"/>
+    <col min="6" max="6" width="14.109375" style="12" customWidth="1"/>
+    <col min="7" max="7" width="14.88671875" style="12" customWidth="1"/>
+    <col min="8" max="8" width="14.5546875" style="12" customWidth="1"/>
+    <col min="9" max="9" width="13.44140625" style="12" customWidth="1"/>
+    <col min="10" max="10" width="13.6640625" style="12" customWidth="1"/>
+    <col min="11" max="11" width="15" style="12" customWidth="1"/>
+    <col min="12" max="12" width="13.6640625" style="12" customWidth="1"/>
     <col min="13" max="13" width="28.33203125" style="9" customWidth="1"/>
     <col min="14" max="14" width="20.109375" style="9" customWidth="1"/>
     <col min="15" max="15" width="17.109375" style="9" customWidth="1"/>
@@ -1685,7 +1766,7 @@
       <c r="E2" t="s">
         <v>78</v>
       </c>
-      <c r="G2" s="9">
+      <c r="G2" s="12">
         <v>1</v>
       </c>
     </row>
@@ -1705,7 +1786,7 @@
       <c r="E3" t="s">
         <v>78</v>
       </c>
-      <c r="G3" s="9">
+      <c r="G3" s="12">
         <v>1</v>
       </c>
     </row>
@@ -1725,7 +1806,7 @@
       <c r="E4" t="s">
         <v>79</v>
       </c>
-      <c r="H4" s="9">
+      <c r="H4" s="12">
         <v>1</v>
       </c>
     </row>
@@ -1745,7 +1826,7 @@
       <c r="E5" t="s">
         <v>79</v>
       </c>
-      <c r="H5" s="9">
+      <c r="H5" s="12">
         <v>1</v>
       </c>
     </row>
@@ -1765,7 +1846,7 @@
       <c r="E6" t="s">
         <v>80</v>
       </c>
-      <c r="H6" s="10">
+      <c r="H6" s="15">
         <v>3</v>
       </c>
     </row>
@@ -1785,7 +1866,7 @@
       <c r="E7" t="s">
         <v>80</v>
       </c>
-      <c r="H7" s="10">
+      <c r="H7" s="15">
         <v>3</v>
       </c>
     </row>
@@ -1805,7 +1886,7 @@
       <c r="E8" t="s">
         <v>81</v>
       </c>
-      <c r="H8" s="10">
+      <c r="H8" s="15">
         <v>2</v>
       </c>
     </row>
@@ -1825,7 +1906,7 @@
       <c r="E9" t="s">
         <v>81</v>
       </c>
-      <c r="H9" s="9">
+      <c r="H9" s="12">
         <v>2</v>
       </c>
     </row>
@@ -1845,7 +1926,7 @@
       <c r="E10" t="s">
         <v>82</v>
       </c>
-      <c r="G10" s="9">
+      <c r="G10" s="12">
         <v>2</v>
       </c>
     </row>
@@ -1865,7 +1946,7 @@
       <c r="E11" t="s">
         <v>82</v>
       </c>
-      <c r="G11" s="9">
+      <c r="G11" s="12">
         <v>2</v>
       </c>
     </row>
@@ -1885,7 +1966,7 @@
       <c r="E12" t="s">
         <v>83</v>
       </c>
-      <c r="I12" s="9">
+      <c r="I12" s="12">
         <v>1</v>
       </c>
     </row>
@@ -1905,7 +1986,7 @@
       <c r="E13" t="s">
         <v>83</v>
       </c>
-      <c r="I13" s="9">
+      <c r="I13" s="12">
         <v>1</v>
       </c>
     </row>
@@ -1925,7 +2006,7 @@
       <c r="E14" t="s">
         <v>84</v>
       </c>
-      <c r="I14" s="9">
+      <c r="I14" s="12">
         <v>2</v>
       </c>
     </row>
@@ -1945,7 +2026,7 @@
       <c r="E15" t="s">
         <v>84</v>
       </c>
-      <c r="I15" s="9">
+      <c r="I15" s="12">
         <v>2</v>
       </c>
     </row>
@@ -1965,11 +2046,11 @@
       <c r="E16" t="s">
         <v>85</v>
       </c>
-      <c r="I16" s="9">
+      <c r="I16" s="12">
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>26</v>
       </c>
@@ -1985,11 +2066,11 @@
       <c r="E17" t="s">
         <v>89</v>
       </c>
-      <c r="I17" s="9">
+      <c r="I17" s="12">
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>27</v>
       </c>
@@ -2005,11 +2086,11 @@
       <c r="E18" t="s">
         <v>89</v>
       </c>
-      <c r="I18" s="9">
+      <c r="I18" s="12">
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>23</v>
       </c>
@@ -2025,11 +2106,11 @@
       <c r="E19" t="s">
         <v>86</v>
       </c>
-      <c r="G19" s="9">
+      <c r="G19" s="12">
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:11" s="11" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" s="10" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>39</v>
       </c>
@@ -2045,16 +2126,17 @@
       <c r="E20" t="s">
         <v>86</v>
       </c>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9">
+      <c r="F20" s="12"/>
+      <c r="G20" s="12">
         <v>3</v>
       </c>
-      <c r="H20" s="9"/>
-      <c r="I20" s="9"/>
-      <c r="J20" s="9"/>
-      <c r="K20" s="9"/>
-    </row>
-    <row r="21" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H20" s="12"/>
+      <c r="I20" s="12"/>
+      <c r="J20" s="12"/>
+      <c r="K20" s="12"/>
+      <c r="L20" s="14"/>
+    </row>
+    <row r="21" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>44</v>
       </c>
@@ -2070,11 +2152,11 @@
       <c r="E21" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="J21" s="9">
+      <c r="J21" s="12">
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>45</v>
       </c>
@@ -2090,12 +2172,11 @@
       <c r="E22" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="J22" s="9">
+      <c r="J22" s="12">
         <v>1</v>
       </c>
-      <c r="K22" s="1"/>
-    </row>
-    <row r="23" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>36</v>
       </c>
@@ -2111,11 +2192,11 @@
       <c r="E23" t="s">
         <v>90</v>
       </c>
-      <c r="G23" s="9">
+      <c r="G23" s="12">
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>31</v>
       </c>
@@ -2131,11 +2212,11 @@
       <c r="E24" t="s">
         <v>91</v>
       </c>
-      <c r="H24" s="9">
+      <c r="H24" s="12">
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>38</v>
       </c>
@@ -2151,11 +2232,11 @@
       <c r="E25" t="s">
         <v>91</v>
       </c>
-      <c r="H25" s="9">
+      <c r="H25" s="12">
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>22</v>
       </c>
@@ -2171,11 +2252,11 @@
       <c r="E26" t="s">
         <v>92</v>
       </c>
-      <c r="I26" s="9">
+      <c r="I26" s="12">
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>28</v>
       </c>
@@ -2191,11 +2272,11 @@
       <c r="E27" t="s">
         <v>92</v>
       </c>
-      <c r="I27" s="9">
+      <c r="I27" s="12">
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>13</v>
       </c>
@@ -2211,11 +2292,11 @@
       <c r="E28" t="s">
         <v>93</v>
       </c>
-      <c r="H28" s="9">
+      <c r="H28" s="12">
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>14</v>
       </c>
@@ -2231,11 +2312,11 @@
       <c r="E29" t="s">
         <v>93</v>
       </c>
-      <c r="H29" s="9">
+      <c r="H29" s="12">
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>3</v>
       </c>
@@ -2251,11 +2332,11 @@
       <c r="E30" t="s">
         <v>94</v>
       </c>
-      <c r="H30" s="9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H30" s="12">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>6</v>
       </c>
@@ -2271,11 +2352,11 @@
       <c r="E31" t="s">
         <v>94</v>
       </c>
-      <c r="H31" s="9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H31" s="12">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>43</v>
       </c>
@@ -2291,175 +2372,222 @@
       <c r="E32" t="s">
         <v>95</v>
       </c>
-      <c r="I32" s="9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33">
+      <c r="I32" s="12">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
+        <v>46</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1">
+        <v>18</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="J33" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34">
         <v>1</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B34" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C33" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34">
+      <c r="C34" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35">
         <v>2</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B35" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C34" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35">
+      <c r="C35" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36">
         <v>5</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="B36" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C35" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36">
+      <c r="C36" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37">
         <v>12</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="B37" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37">
-        <v>15</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>21</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="38" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="39" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="40" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40">
+        <v>21</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="41" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41">
         <v>24</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B41" t="s">
         <v>31</v>
       </c>
-      <c r="C40" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41">
-        <v>29</v>
-      </c>
-      <c r="B41" t="s">
+      <c r="C41" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="42" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>29</v>
+      </c>
+      <c r="B42" t="s">
         <v>36</v>
       </c>
-      <c r="C41" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42">
+      <c r="C42" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="43" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43">
         <v>30</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B43" t="s">
         <v>37</v>
       </c>
-      <c r="C42" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43">
+      <c r="C43" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="44" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44">
         <v>32</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B44" t="s">
         <v>39</v>
       </c>
-      <c r="C43" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44">
+      <c r="C44" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="45" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45">
         <v>34</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B45" t="s">
         <v>41</v>
       </c>
-      <c r="C44" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45">
+      <c r="C45" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="46" spans="1:31" s="1" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A46">
         <v>35</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B46" t="s">
         <v>42</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" s="1" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A46">
-        <v>41</v>
-      </c>
-      <c r="B46" t="s">
-        <v>48</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D46"/>
       <c r="E46"/>
-      <c r="F46" s="9"/>
-      <c r="G46" s="9"/>
-      <c r="H46" s="9"/>
-      <c r="I46" s="9"/>
-      <c r="J46" s="9"/>
-      <c r="K46" s="9"/>
+      <c r="F46" s="12"/>
+      <c r="G46" s="12"/>
+      <c r="H46" s="12"/>
+      <c r="I46" s="12"/>
+      <c r="J46" s="12"/>
+      <c r="K46" s="12"/>
+      <c r="L46" s="12"/>
+    </row>
+    <row r="47" spans="1:31" s="1" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>41</v>
+      </c>
+      <c r="B47" t="s">
+        <v>48</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D47"/>
+      <c r="E47"/>
+      <c r="F47" s="12"/>
+      <c r="G47" s="12"/>
+      <c r="H47" s="12"/>
+      <c r="I47" s="12"/>
+      <c r="J47" s="12"/>
+      <c r="K47" s="12"/>
+      <c r="L47" s="12"/>
+      <c r="M47" s="12"/>
+      <c r="N47" s="12"/>
+      <c r="O47" s="12"/>
+      <c r="P47" s="12"/>
+      <c r="Q47" s="12"/>
+      <c r="R47" s="12"/>
+      <c r="S47" s="12"/>
+      <c r="T47" s="12"/>
+      <c r="U47" s="12"/>
+      <c r="V47" s="12"/>
+      <c r="W47" s="12"/>
+      <c r="X47" s="12"/>
+      <c r="Y47" s="12"/>
+      <c r="Z47" s="12"/>
+      <c r="AA47" s="12"/>
+      <c r="AB47" s="12"/>
+      <c r="AC47" s="12"/>
+      <c r="AD47" s="12"/>
+      <c r="AE47" s="12"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:K1">
-    <sortState ref="A2:K46">
+    <sortState ref="A2:K47">
       <sortCondition ref="D1"/>
     </sortState>
   </autoFilter>
